--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,26 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pad Pos 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.63885</v>
+        <v>16.81387</v>
       </c>
       <c r="D2" t="n">
-        <v>16.60816</v>
+        <v>16.57063</v>
       </c>
       <c r="E2" t="n">
-        <v>16.78479</v>
+        <v>16.67055</v>
       </c>
       <c r="F2" t="n">
-        <v>42.04799</v>
+        <v>41.88107</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05065</v>
+        <v>0.05093</v>
       </c>
       <c r="H2" t="n">
-        <v>1.79521</v>
+        <v>1.86262</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.67551</v>
+        <v>16.90078</v>
       </c>
       <c r="D3" t="n">
-        <v>16.79292</v>
+        <v>16.17715</v>
       </c>
       <c r="E3" t="n">
-        <v>16.24639</v>
+        <v>16.67637</v>
       </c>
       <c r="F3" t="n">
-        <v>42.67142</v>
+        <v>43.48405</v>
       </c>
       <c r="G3" t="n">
-        <v>0.051</v>
+        <v>0.05114</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81535</v>
+        <v>1.846</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.5885</v>
+        <v>16.94098</v>
       </c>
       <c r="D4" t="n">
-        <v>16.4708</v>
+        <v>16.57518</v>
       </c>
       <c r="E4" t="n">
-        <v>16.95331</v>
+        <v>16.67759</v>
       </c>
       <c r="F4" t="n">
-        <v>43.16346</v>
+        <v>41.84181</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05091</v>
+        <v>0.05051</v>
       </c>
       <c r="H4" t="n">
-        <v>1.80348</v>
+        <v>1.81835</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.76455</v>
+        <v>16.8403</v>
       </c>
       <c r="D5" t="n">
-        <v>16.53721</v>
+        <v>16.57163</v>
       </c>
       <c r="E5" t="n">
-        <v>16.84565</v>
+        <v>16.82231</v>
       </c>
       <c r="F5" t="n">
-        <v>41.86477</v>
+        <v>41.98811</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05057</v>
+        <v>0.05047</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8156</v>
+        <v>1.79436</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.68811</v>
+        <v>16.7744</v>
       </c>
       <c r="D6" t="n">
-        <v>16.77001</v>
+        <v>16.53659</v>
       </c>
       <c r="E6" t="n">
-        <v>16.86754</v>
+        <v>16.67455</v>
       </c>
       <c r="F6" t="n">
-        <v>42.0265</v>
+        <v>42.32487</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05005</v>
+        <v>0.05096</v>
       </c>
       <c r="H6" t="n">
-        <v>1.84173</v>
+        <v>1.8616</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.64712</v>
+        <v>16.88323</v>
       </c>
       <c r="D7" t="n">
-        <v>16.26883</v>
+        <v>16.50504</v>
       </c>
       <c r="E7" t="n">
-        <v>16.70309</v>
+        <v>16.76976</v>
       </c>
       <c r="F7" t="n">
-        <v>42.32044</v>
+        <v>42.24105</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0505</v>
+        <v>0.04955</v>
       </c>
       <c r="H7" t="n">
-        <v>1.80107</v>
+        <v>1.80984</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.32435</v>
+        <v>16.89468</v>
       </c>
       <c r="D8" t="n">
-        <v>16.54346</v>
+        <v>16.76671</v>
       </c>
       <c r="E8" t="n">
-        <v>16.46839</v>
+        <v>16.83237</v>
       </c>
       <c r="F8" t="n">
-        <v>42.93537</v>
+        <v>41.934</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0496</v>
+        <v>0.05095</v>
       </c>
       <c r="H8" t="n">
-        <v>1.82346</v>
+        <v>1.85624</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.96054</v>
+        <v>16.6771</v>
       </c>
       <c r="D9" t="n">
-        <v>16.42397</v>
+        <v>16.37659</v>
       </c>
       <c r="E9" t="n">
-        <v>17.08503</v>
+        <v>16.57318</v>
       </c>
       <c r="F9" t="n">
-        <v>42.15096</v>
+        <v>42.04039</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04965</v>
+        <v>0.05077</v>
       </c>
       <c r="H9" t="n">
-        <v>1.82585</v>
+        <v>1.80405</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.87951</v>
+        <v>16.89742</v>
       </c>
       <c r="D10" t="n">
-        <v>16.59475</v>
+        <v>16.202</v>
       </c>
       <c r="E10" t="n">
-        <v>16.7922</v>
+        <v>16.6468</v>
       </c>
       <c r="F10" t="n">
-        <v>42.54534</v>
+        <v>42.42694</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05015</v>
+        <v>0.04927</v>
       </c>
       <c r="H10" t="n">
-        <v>1.84324</v>
+        <v>1.79446</v>
       </c>
     </row>
     <row r="11">
@@ -718,26 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad Pos 2</t>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.831</v>
+        <v>16.94158</v>
       </c>
       <c r="D12" t="n">
-        <v>16.63779</v>
+        <v>16.53816</v>
       </c>
       <c r="E12" t="n">
-        <v>16.93016</v>
+        <v>16.87571</v>
       </c>
       <c r="F12" t="n">
-        <v>42.48128</v>
+        <v>41.26495</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05117</v>
+        <v>0.05023</v>
       </c>
       <c r="H12" t="n">
-        <v>1.82427</v>
+        <v>1.83891</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.13301</v>
+        <v>17.093</v>
       </c>
       <c r="D13" t="n">
-        <v>16.90338</v>
+        <v>16.33738</v>
       </c>
       <c r="E13" t="n">
-        <v>16.36929</v>
+        <v>16.48815</v>
       </c>
       <c r="F13" t="n">
-        <v>42.17389</v>
+        <v>41.35911</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05009</v>
+        <v>0.04976</v>
       </c>
       <c r="H13" t="n">
-        <v>1.80867</v>
+        <v>1.84956</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.15136</v>
+        <v>16.99705</v>
       </c>
       <c r="D14" t="n">
-        <v>16.49623</v>
+        <v>16.66567</v>
       </c>
       <c r="E14" t="n">
-        <v>16.5142</v>
+        <v>16.87236</v>
       </c>
       <c r="F14" t="n">
-        <v>42.48946</v>
+        <v>41.99119</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0515</v>
+        <v>0.05063</v>
       </c>
       <c r="H14" t="n">
-        <v>1.79858</v>
+        <v>1.81499</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.96757</v>
+        <v>16.92637</v>
       </c>
       <c r="D15" t="n">
-        <v>16.67678</v>
+        <v>16.25657</v>
       </c>
       <c r="E15" t="n">
-        <v>16.70878</v>
+        <v>16.31297</v>
       </c>
       <c r="F15" t="n">
-        <v>42.86685</v>
+        <v>42.99533</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0497</v>
+        <v>0.05209</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8103</v>
+        <v>1.82061</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.68063</v>
+        <v>16.68368</v>
       </c>
       <c r="D16" t="n">
-        <v>16.72446</v>
+        <v>16.49241</v>
       </c>
       <c r="E16" t="n">
-        <v>16.73922</v>
+        <v>16.67016</v>
       </c>
       <c r="F16" t="n">
-        <v>42.24068</v>
+        <v>42.80295</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05054</v>
+        <v>0.05029</v>
       </c>
       <c r="H16" t="n">
-        <v>1.81663</v>
+        <v>1.8216</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.56605</v>
+        <v>17.06087</v>
       </c>
       <c r="D17" t="n">
-        <v>16.38538</v>
+        <v>16.70555</v>
       </c>
       <c r="E17" t="n">
-        <v>16.59329</v>
+        <v>16.81906</v>
       </c>
       <c r="F17" t="n">
-        <v>43.18421</v>
+        <v>41.94787</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05079</v>
+        <v>0.05053</v>
       </c>
       <c r="H17" t="n">
-        <v>1.84041</v>
+        <v>1.83482</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.63777</v>
+        <v>16.83607</v>
       </c>
       <c r="D18" t="n">
-        <v>16.33719</v>
+        <v>16.50917</v>
       </c>
       <c r="E18" t="n">
-        <v>16.43927</v>
+        <v>16.5769</v>
       </c>
       <c r="F18" t="n">
-        <v>42.33719</v>
+        <v>41.76532</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05016</v>
+        <v>0.04984</v>
       </c>
       <c r="H18" t="n">
-        <v>1.79882</v>
+        <v>1.81296</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.07537</v>
+        <v>17.00776</v>
       </c>
       <c r="D19" t="n">
-        <v>16.3735</v>
+        <v>16.18386</v>
       </c>
       <c r="E19" t="n">
-        <v>16.70479</v>
+        <v>16.9309</v>
       </c>
       <c r="F19" t="n">
-        <v>42.73622</v>
+        <v>42.96641</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05017</v>
+        <v>0.05195</v>
       </c>
       <c r="H19" t="n">
-        <v>1.80998</v>
+        <v>1.79395</v>
       </c>
     </row>
     <row r="20">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.9416</v>
+        <v>16.88618</v>
       </c>
       <c r="D20" t="n">
-        <v>16.98395</v>
+        <v>16.46246</v>
       </c>
       <c r="E20" t="n">
-        <v>17.09283</v>
+        <v>16.59682</v>
       </c>
       <c r="F20" t="n">
-        <v>43.31449</v>
+        <v>42.46496</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05104</v>
+        <v>0.04945</v>
       </c>
       <c r="H20" t="n">
-        <v>1.84588</v>
+        <v>1.80968</v>
       </c>
     </row>
     <row r="21">
@@ -970,20 +970,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SR Pad Pos 1</t>
+          <t>SR Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.71377</v>
+        <v>15.65115</v>
       </c>
       <c r="D22" t="n">
-        <v>15.51676</v>
+        <v>15.42167</v>
       </c>
       <c r="E22" t="n">
-        <v>15.78892</v>
+        <v>15.51047</v>
       </c>
       <c r="F22" t="n">
-        <v>255.46323</v>
+        <v>250.83163</v>
       </c>
     </row>
     <row r="23">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15.72077</v>
+        <v>15.6998</v>
       </c>
       <c r="D23" t="n">
-        <v>15.73231</v>
+        <v>15.43185</v>
       </c>
       <c r="E23" t="n">
-        <v>15.63724</v>
+        <v>15.61151</v>
       </c>
       <c r="F23" t="n">
-        <v>253.5335</v>
+        <v>254.36236</v>
       </c>
     </row>
     <row r="24">
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15.49548</v>
+        <v>15.71767</v>
       </c>
       <c r="D24" t="n">
-        <v>15.6644</v>
+        <v>15.43604</v>
       </c>
       <c r="E24" t="n">
-        <v>15.52314</v>
+        <v>15.6461</v>
       </c>
       <c r="F24" t="n">
-        <v>252.26175</v>
+        <v>255.7391</v>
       </c>
     </row>
     <row r="25">
@@ -1031,16 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15.39435</v>
+        <v>15.6004</v>
       </c>
       <c r="D25" t="n">
-        <v>15.80352</v>
+        <v>15.40886</v>
       </c>
       <c r="E25" t="n">
-        <v>15.60537</v>
+        <v>15.51771</v>
       </c>
       <c r="F25" t="n">
-        <v>256.45996</v>
+        <v>252.54354</v>
       </c>
     </row>
     <row r="26">
@@ -1050,16 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15.37343</v>
+        <v>15.87135</v>
       </c>
       <c r="D26" t="n">
-        <v>15.15779</v>
+        <v>15.16329</v>
       </c>
       <c r="E26" t="n">
-        <v>15.55409</v>
+        <v>15.69699</v>
       </c>
       <c r="F26" t="n">
-        <v>253.22671</v>
+        <v>256.44262</v>
       </c>
     </row>
     <row r="27">
@@ -1069,16 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>15.61688</v>
+        <v>15.63221</v>
       </c>
       <c r="D27" t="n">
-        <v>15.67718</v>
+        <v>15.38933</v>
       </c>
       <c r="E27" t="n">
-        <v>15.61831</v>
+        <v>15.5167</v>
       </c>
       <c r="F27" t="n">
-        <v>252.0997</v>
+        <v>258.30685</v>
       </c>
     </row>
     <row r="28">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>15.49668</v>
+        <v>15.92937</v>
       </c>
       <c r="D28" t="n">
-        <v>15.71814</v>
+        <v>15.47989</v>
       </c>
       <c r="E28" t="n">
-        <v>15.72444</v>
+        <v>15.68073</v>
       </c>
       <c r="F28" t="n">
-        <v>248.49048</v>
+        <v>253.89208</v>
       </c>
     </row>
     <row r="29">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>15.77288</v>
+        <v>15.72261</v>
       </c>
       <c r="D29" t="n">
-        <v>15.55868</v>
+        <v>15.40026</v>
       </c>
       <c r="E29" t="n">
-        <v>15.13581</v>
+        <v>15.62968</v>
       </c>
       <c r="F29" t="n">
-        <v>257.95475</v>
+        <v>254.2834</v>
       </c>
     </row>
     <row r="30">
@@ -1126,16 +1126,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>15.70118</v>
+        <v>15.79857</v>
       </c>
       <c r="D30" t="n">
-        <v>15.57936</v>
+        <v>15.48174</v>
       </c>
       <c r="E30" t="n">
-        <v>15.35419</v>
+        <v>15.63432</v>
       </c>
       <c r="F30" t="n">
-        <v>252.11283</v>
+        <v>256.99993</v>
       </c>
     </row>
     <row r="31">
@@ -1173,23 +1173,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Trace Pos 1</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>16.81004</v>
+        <v>16.57553</v>
       </c>
       <c r="D32" t="n">
-        <v>16.17413</v>
+        <v>15.81606</v>
       </c>
       <c r="E32" t="n">
-        <v>16.56736</v>
+        <v>16.51041</v>
       </c>
       <c r="F32" t="n">
-        <v>21.81743</v>
+        <v>21.56103</v>
       </c>
       <c r="G32" t="n">
-        <v>34.03942</v>
+        <v>33.52966</v>
       </c>
     </row>
     <row r="33">
@@ -1199,19 +1199,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>16.58131</v>
+        <v>16.70309</v>
       </c>
       <c r="D33" t="n">
-        <v>15.97307</v>
+        <v>15.92055</v>
       </c>
       <c r="E33" t="n">
-        <v>16.26713</v>
+        <v>16.36119</v>
       </c>
       <c r="F33" t="n">
-        <v>21.99539</v>
+        <v>21.51276</v>
       </c>
       <c r="G33" t="n">
-        <v>34.12916</v>
+        <v>35.27488</v>
       </c>
     </row>
     <row r="34">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>16.8171</v>
+        <v>16.64434</v>
       </c>
       <c r="D34" t="n">
-        <v>15.78922</v>
+        <v>15.76973</v>
       </c>
       <c r="E34" t="n">
-        <v>16.3516</v>
+        <v>16.56078</v>
       </c>
       <c r="F34" t="n">
-        <v>21.69308</v>
+        <v>21.32711</v>
       </c>
       <c r="G34" t="n">
-        <v>34.17553</v>
+        <v>34.24054</v>
       </c>
     </row>
     <row r="35">
@@ -1243,19 +1243,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>16.38335</v>
+        <v>16.85837</v>
       </c>
       <c r="D35" t="n">
-        <v>16.23947</v>
+        <v>15.8231</v>
       </c>
       <c r="E35" t="n">
-        <v>16.4469</v>
+        <v>16.77439</v>
       </c>
       <c r="F35" t="n">
-        <v>22.04841</v>
+        <v>21.57728</v>
       </c>
       <c r="G35" t="n">
-        <v>34.14315</v>
+        <v>33.56132</v>
       </c>
     </row>
     <row r="36">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>16.63252</v>
+        <v>16.737</v>
       </c>
       <c r="D36" t="n">
-        <v>15.88333</v>
+        <v>16.06604</v>
       </c>
       <c r="E36" t="n">
-        <v>16.37115</v>
+        <v>16.39238</v>
       </c>
       <c r="F36" t="n">
-        <v>21.52579</v>
+        <v>21.88074</v>
       </c>
       <c r="G36" t="n">
-        <v>34.27515</v>
+        <v>34.23887</v>
       </c>
     </row>
     <row r="37">
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>16.56168</v>
+        <v>16.54912</v>
       </c>
       <c r="D37" t="n">
-        <v>16.37289</v>
+        <v>16.17954</v>
       </c>
       <c r="E37" t="n">
-        <v>16.69115</v>
+        <v>16.42544</v>
       </c>
       <c r="F37" t="n">
-        <v>21.6663</v>
+        <v>21.81174</v>
       </c>
       <c r="G37" t="n">
-        <v>34.37365</v>
+        <v>34.68118</v>
       </c>
     </row>
     <row r="38">
@@ -1309,19 +1309,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>16.73066</v>
+        <v>16.68907</v>
       </c>
       <c r="D38" t="n">
-        <v>15.59626</v>
+        <v>16.17057</v>
       </c>
       <c r="E38" t="n">
-        <v>16.26322</v>
+        <v>16.41843</v>
       </c>
       <c r="F38" t="n">
-        <v>21.76901</v>
+        <v>22.19034</v>
       </c>
       <c r="G38" t="n">
-        <v>34.59183</v>
+        <v>34.83746</v>
       </c>
     </row>
     <row r="39">
@@ -1331,19 +1331,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>16.98259</v>
+        <v>16.36929</v>
       </c>
       <c r="D39" t="n">
-        <v>16.2119</v>
+        <v>15.86542</v>
       </c>
       <c r="E39" t="n">
-        <v>16.18597</v>
+        <v>16.23055</v>
       </c>
       <c r="F39" t="n">
-        <v>21.84515</v>
+        <v>21.60358</v>
       </c>
       <c r="G39" t="n">
-        <v>33.94479</v>
+        <v>34.92265</v>
       </c>
     </row>
     <row r="40">
@@ -1353,30 +1353,45 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>16.63383</v>
+        <v>16.59681</v>
       </c>
       <c r="D40" t="n">
-        <v>15.7303</v>
+        <v>15.81359</v>
       </c>
       <c r="E40" t="n">
-        <v>16.01911</v>
+        <v>16.38879</v>
       </c>
       <c r="F40" t="n">
-        <v>21.74829</v>
+        <v>22.14595</v>
       </c>
       <c r="G40" t="n">
-        <v>34.29333</v>
+        <v>33.77336</v>
       </c>
     </row>
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dimple</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Bump</t>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -1388,14 +1403,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Via Pos 1</t>
+          <t>Trace 2</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.60593</v>
+        <v>16.86536</v>
       </c>
       <c r="D42" t="n">
-        <v>1.09818</v>
+        <v>16.06666</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.40498</v>
+      </c>
+      <c r="F42" t="n">
+        <v>21.94375</v>
+      </c>
+      <c r="G42" t="n">
+        <v>33.59976</v>
       </c>
     </row>
     <row r="43">
@@ -1405,10 +1429,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.5937</v>
+        <v>16.59446</v>
       </c>
       <c r="D43" t="n">
-        <v>1.13201</v>
+        <v>15.87674</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.5205</v>
+      </c>
+      <c r="F43" t="n">
+        <v>21.81172</v>
+      </c>
+      <c r="G43" t="n">
+        <v>33.99369</v>
       </c>
     </row>
     <row r="44">
@@ -1418,10 +1451,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.60734</v>
+        <v>16.67659</v>
       </c>
       <c r="D44" t="n">
-        <v>1.12364</v>
+        <v>15.94601</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.16686</v>
+      </c>
+      <c r="F44" t="n">
+        <v>21.48084</v>
+      </c>
+      <c r="G44" t="n">
+        <v>33.9911</v>
       </c>
     </row>
     <row r="45">
@@ -1431,10 +1473,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.60619</v>
+        <v>16.96523</v>
       </c>
       <c r="D45" t="n">
-        <v>1.13956</v>
+        <v>16.04895</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.56368</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.54892</v>
+      </c>
+      <c r="G45" t="n">
+        <v>33.67056</v>
       </c>
     </row>
     <row r="46">
@@ -1444,10 +1495,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.61126</v>
+        <v>16.43927</v>
       </c>
       <c r="D46" t="n">
-        <v>1.11947</v>
+        <v>15.92685</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.25119</v>
+      </c>
+      <c r="F46" t="n">
+        <v>21.48586</v>
+      </c>
+      <c r="G46" t="n">
+        <v>34.76792</v>
       </c>
     </row>
     <row r="47">
@@ -1457,10 +1517,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.611</v>
+        <v>16.48397</v>
       </c>
       <c r="D47" t="n">
-        <v>1.12717</v>
+        <v>15.9961</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.47334</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21.57214</v>
+      </c>
+      <c r="G47" t="n">
+        <v>33.98748</v>
       </c>
     </row>
     <row r="48">
@@ -1470,10 +1539,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.60373</v>
+        <v>16.83955</v>
       </c>
       <c r="D48" t="n">
-        <v>1.10069</v>
+        <v>16.36259</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.78205</v>
+      </c>
+      <c r="F48" t="n">
+        <v>22.17289</v>
+      </c>
+      <c r="G48" t="n">
+        <v>34.50262</v>
       </c>
     </row>
     <row r="49">
@@ -1483,10 +1561,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.61097</v>
+        <v>16.92059</v>
       </c>
       <c r="D49" t="n">
-        <v>1.13214</v>
+        <v>16.0179</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.32283</v>
+      </c>
+      <c r="F49" t="n">
+        <v>21.97163</v>
+      </c>
+      <c r="G49" t="n">
+        <v>34.34629</v>
       </c>
     </row>
     <row r="50">
@@ -1496,31 +1583,30 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.60177</v>
+        <v>16.73501</v>
       </c>
       <c r="D50" t="n">
-        <v>1.10798</v>
+        <v>16.14094</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.39633</v>
+      </c>
+      <c r="F50" t="n">
+        <v>21.68246</v>
+      </c>
+      <c r="G50" t="n">
+        <v>33.79015</v>
       </c>
     </row>
     <row r="51">
       <c r="C51" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Radius</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -1532,20 +1618,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Landing Pad 1</t>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>16.99902</v>
+        <v>0.6103</v>
       </c>
       <c r="D52" t="n">
-        <v>16.65994</v>
-      </c>
-      <c r="E52" t="n">
-        <v>16.58897</v>
-      </c>
-      <c r="F52" t="n">
-        <v>42.72825</v>
+        <v>1.10521</v>
       </c>
     </row>
     <row r="53">
@@ -1555,16 +1635,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>17.06507</v>
+        <v>0.60206</v>
       </c>
       <c r="D53" t="n">
-        <v>16.43426</v>
-      </c>
-      <c r="E53" t="n">
-        <v>16.32357</v>
-      </c>
-      <c r="F53" t="n">
-        <v>42.18882</v>
+        <v>1.0925</v>
       </c>
     </row>
     <row r="54">
@@ -1574,16 +1648,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>16.77714</v>
+        <v>0.61572</v>
       </c>
       <c r="D54" t="n">
-        <v>16.42367</v>
-      </c>
-      <c r="E54" t="n">
-        <v>16.57712</v>
-      </c>
-      <c r="F54" t="n">
-        <v>43.13409</v>
+        <v>1.11106</v>
       </c>
     </row>
     <row r="55">
@@ -1593,16 +1661,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>16.79664</v>
+        <v>0.61208</v>
       </c>
       <c r="D55" t="n">
-        <v>16.81941</v>
-      </c>
-      <c r="E55" t="n">
-        <v>16.90885</v>
-      </c>
-      <c r="F55" t="n">
-        <v>42.01064</v>
+        <v>1.09102</v>
       </c>
     </row>
     <row r="56">
@@ -1612,16 +1674,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>16.79136</v>
+        <v>0.59056</v>
       </c>
       <c r="D56" t="n">
-        <v>16.26981</v>
-      </c>
-      <c r="E56" t="n">
-        <v>16.5279</v>
-      </c>
-      <c r="F56" t="n">
-        <v>42.86882</v>
+        <v>1.10741</v>
       </c>
     </row>
     <row r="57">
@@ -1631,16 +1687,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>16.83075</v>
+        <v>0.60436</v>
       </c>
       <c r="D57" t="n">
-        <v>16.53017</v>
-      </c>
-      <c r="E57" t="n">
-        <v>16.89734</v>
-      </c>
-      <c r="F57" t="n">
-        <v>41.60649</v>
+        <v>1.1083</v>
       </c>
     </row>
     <row r="58">
@@ -1650,16 +1700,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>16.30489</v>
+        <v>0.6108</v>
       </c>
       <c r="D58" t="n">
-        <v>16.55901</v>
-      </c>
-      <c r="E58" t="n">
-        <v>16.77037</v>
-      </c>
-      <c r="F58" t="n">
-        <v>42.86088</v>
+        <v>1.11198</v>
       </c>
     </row>
     <row r="59">
@@ -1669,16 +1713,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>16.68749</v>
+        <v>0.60167</v>
       </c>
       <c r="D59" t="n">
-        <v>16.93667</v>
-      </c>
-      <c r="E59" t="n">
-        <v>16.35258</v>
-      </c>
-      <c r="F59" t="n">
-        <v>42.22832</v>
+        <v>1.09976</v>
       </c>
     </row>
     <row r="60">
@@ -1688,57 +1726,21 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>16.40816</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>16.62524</v>
-      </c>
-      <c r="E60" t="n">
-        <v>17.08975</v>
-      </c>
-      <c r="F60" t="n">
-        <v>42.125</v>
+        <v>1.11954</v>
       </c>
     </row>
     <row r="61">
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1752,14 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>via 2</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.74266</v>
+        <v>0.59306</v>
       </c>
       <c r="D62" t="n">
-        <v>0.08101</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0.613</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0.9695</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0.10963</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.00759</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0.09246</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0.12676</v>
+        <v>1.11937</v>
       </c>
     </row>
     <row r="63">
@@ -1785,28 +1769,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.75199</v>
+        <v>0.6061800000000001</v>
       </c>
       <c r="D63" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0.59758</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.9523</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0.11055</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.00756</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0.09185</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0.12756</v>
+        <v>1.07763</v>
       </c>
     </row>
     <row r="64">
@@ -1816,28 +1782,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.74504</v>
+        <v>0.61564</v>
       </c>
       <c r="D64" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0.60859</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.96785</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0.11232</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.00764</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0.09470000000000001</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0.12751</v>
+        <v>1.11428</v>
       </c>
     </row>
     <row r="65">
@@ -1847,28 +1795,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.76412</v>
+        <v>0.60699</v>
       </c>
       <c r="D65" t="n">
-        <v>0.08001999999999999</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0.60217</v>
-      </c>
-      <c r="F65" t="n">
-        <v>0.97454</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0.10725</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.00756</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0.09361999999999999</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0.126</v>
+        <v>1.09318</v>
       </c>
     </row>
     <row r="66">
@@ -1878,28 +1808,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.76165</v>
+        <v>0.6017</v>
       </c>
       <c r="D66" t="n">
-        <v>0.08051999999999999</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0.60054</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0.96231</v>
-      </c>
-      <c r="G66" t="n">
-        <v>0.10866</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.00772</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0.09318</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0.12846</v>
+        <v>1.12067</v>
       </c>
     </row>
     <row r="67">
@@ -1909,28 +1821,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.74004</v>
+        <v>0.61421</v>
       </c>
       <c r="D67" t="n">
-        <v>0.08033999999999999</v>
-      </c>
-      <c r="E67" t="n">
-        <v>0.60706</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0.9413899999999999</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0.10896</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0.00745</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0.09225</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0.12642</v>
+        <v>1.12494</v>
       </c>
     </row>
     <row r="68">
@@ -1940,28 +1834,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.73607</v>
+        <v>0.60886</v>
       </c>
       <c r="D68" t="n">
-        <v>0.08135000000000001</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0.6051</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0.9504</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0.11115</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0.00764</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0.09320000000000001</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0.12528</v>
+        <v>1.10779</v>
       </c>
     </row>
     <row r="69">
@@ -1971,28 +1847,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.75371</v>
+        <v>0.6029600000000001</v>
       </c>
       <c r="D69" t="n">
-        <v>0.08029</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0.60822</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0.97275</v>
-      </c>
-      <c r="G69" t="n">
-        <v>0.10848</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0.00764</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0.09136</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0.12804</v>
+        <v>1.11205</v>
       </c>
     </row>
     <row r="70">
@@ -2002,28 +1860,336 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.75051</v>
+        <v>0.60249</v>
       </c>
       <c r="D70" t="n">
-        <v>0.08219</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0.6014</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0.97177</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0.10852</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0.00757</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0.09225999999999999</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0.12566</v>
+        <v>1.12535</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.74721</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.08154</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.59959</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.95889</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.10897</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.09135</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.12848</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.7512799999999999</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.08204</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.60609</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.95763</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.10857</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.09211</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.12676</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.74277</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.0829</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.61819</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.95735</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.10983</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.09081</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.12549</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.74926</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.08187</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.61755</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.97477</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.10791</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.09239</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.12601</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.73674</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.07911</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.60693</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.96387</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.10907</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.00749</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.09103</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.12864</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.74905</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.08172</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.60619</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.98417</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.11003</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.00763</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.09369</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.12809</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.7446</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.08005</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.61097</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.97776</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.10832</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.00755</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.09421</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.12698</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.74399</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.08139</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.61681</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.95198</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.10685</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.00753</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.09297999999999999</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.12518</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.74346</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.08216</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.60711</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.9743000000000001</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.11068</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.09306</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.12401</v>
       </c>
     </row>
   </sheetData>
